--- a/app/sample_data/sample_establishment_report.xlsx
+++ b/app/sample_data/sample_establishment_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,17 +478,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Sarah Johnson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,11 +503,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -518,17 +518,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Jessica Brown</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,16 +538,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -558,22 +558,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Jessica Brown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uptown High School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Jessica Brown</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,26 +608,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amanda Wilson</t>
+          <t>Sarah Johnson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Uptown High School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -678,17 +678,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Martinez</t>
+          <t>Amanda Wilson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -698,16 +698,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -718,36 +718,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jessica Brown</t>
+          <t>Amanda Wilson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Establishment</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -758,36 +758,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Jessica Brown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -798,17 +798,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>David Martinez</t>
+          <t>Amanda Wilson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -818,16 +818,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -838,22 +838,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Michael Chen</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Midtown Middle School</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -863,11 +863,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -878,27 +878,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Sarah Johnson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Under Review</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Uptown High School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -918,36 +918,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>David Martinez</t>
+          <t>Michael Chen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enforcement</t>
+          <t>Establishment</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -958,7 +958,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>David Martinez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enforcement</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -1008,26 +1008,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>David Martinez</t>
+          <t>Michael Chen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>David Martinez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1098,16 +1098,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Enforcement</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1118,36 +1118,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amanda Wilson</t>
+          <t>David Martinez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1158,17 +1158,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>Amanda Wilson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amanda Wilson</t>
+          <t>Jessica Brown</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22">
@@ -1278,36 +1278,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amanda Wilson</t>
+          <t>Michael Chen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Uptown High School</t>
+          <t>Downtown Elementary</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1363,22 +1363,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Midtown Middle School</t>
+          <t>Uptown High School</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Establishment</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -1398,36 +1398,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Michael Chen</t>
+          <t>David Martinez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Midtown Middle School</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Establishment</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
@@ -1443,22 +1443,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Under Review</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Downtown Elementary</t>
+          <t>Midtown Middle School</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Establishment</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
